--- a/FL-corrections-structure/ig/StructureDefinition-fr-core-location.xlsx
+++ b/FL-corrections-structure/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-08T19:18:35+00:00</t>
+    <t>2026-03-11T17:39:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -730,7 +730,7 @@
     <t>The operational status if the location (where typically a bed/room).</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0116|2.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0116|3.0.0</t>
   </si>
   <si>
     <t>Location.name</t>
